--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -1310,10 +1310,9 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>필수 base</t>
+          <t>베이스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1352,7 +1351,6 @@
           <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1360,7 +1358,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1402,7 +1399,6 @@
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1410,7 +1406,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1452,7 +1447,6 @@
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1460,7 +1454,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1502,7 +1495,6 @@
           <t>분말지방; 믹스 편의·크리미</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1510,7 +1502,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1552,7 +1543,6 @@
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1560,7 +1550,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1602,7 +1591,6 @@
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1610,7 +1598,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1652,7 +1639,6 @@
           <t>경질지방→용해저항·구조(소량 구조재)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1660,7 +1646,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1702,7 +1687,6 @@
           <t>범용 식물지방</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1710,7 +1694,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1752,7 +1735,6 @@
           <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1760,7 +1742,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1802,7 +1783,6 @@
           <t>산화안정 좋은 액상유</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1810,7 +1790,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1852,7 +1831,6 @@
           <t>산화 취약 — 산화취 위험, 지양</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1860,7 +1838,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>지방(유지)</t>
@@ -1881,9 +1858,6 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
@@ -1894,7 +1868,6 @@
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1902,7 +1875,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -1944,7 +1916,6 @@
           <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1952,7 +1923,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -1994,7 +1964,6 @@
           <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2002,7 +1971,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -2044,7 +2012,6 @@
           <t>단맛 보강 극소량(벌크·FPD 없음)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2052,7 +2019,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -2094,7 +2060,6 @@
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2102,7 +2067,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -2144,7 +2108,6 @@
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2152,7 +2115,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -2194,7 +2156,6 @@
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2202,7 +2163,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>감미/빙점</t>
@@ -2244,7 +2204,6 @@
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2252,7 +2211,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>단백</t>
@@ -2294,7 +2252,6 @@
           <t>유화·기포·바디 (단백 결론: 대두단백)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2302,7 +2259,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>단백</t>
@@ -2344,7 +2300,6 @@
           <t>대체 식물단백</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2352,7 +2307,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>단백</t>
@@ -2394,7 +2348,6 @@
           <t>가용성 낮음·그릿티 → 대두로 대체</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2402,7 +2355,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>단백</t>
@@ -2423,9 +2375,6 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
@@ -2436,7 +2385,6 @@
           <t>동물성(비건 아님)</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2444,7 +2392,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2486,7 +2433,6 @@
           <t>얼음결정 억제 주력</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2494,7 +2440,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2536,7 +2481,6 @@
           <t>구아와 시너지·크리미</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2544,7 +2488,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2586,7 +2529,6 @@
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2594,7 +2536,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2636,7 +2577,6 @@
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2644,7 +2584,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2686,7 +2625,6 @@
           <t>오버런·용해저항·동결해동 안정</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2694,7 +2632,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2736,7 +2673,6 @@
           <t>소량 점도(과량시 검성 주의)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2744,7 +2680,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2786,7 +2721,6 @@
           <t>점도·수분결합</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2794,7 +2728,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2836,7 +2769,6 @@
           <t>겔화, 극소량 구조</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2844,7 +2776,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>안정제</t>
@@ -2886,7 +2817,6 @@
           <t>바디·fat replacer</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2894,7 +2824,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -2936,7 +2865,6 @@
           <t>아이스크림 표준 유화제(식물성 선택)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2944,7 +2872,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -2986,7 +2913,6 @@
           <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2994,7 +2920,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3036,7 +2961,6 @@
           <t>고HLB→미세 유화(저HLB와 페어링)</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3044,7 +2968,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3086,7 +3009,6 @@
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3094,7 +3016,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3136,7 +3057,6 @@
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3144,7 +3064,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3186,7 +3105,6 @@
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3194,7 +3112,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3236,7 +3153,6 @@
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3244,7 +3160,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3286,7 +3201,6 @@
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3294,7 +3208,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>유화제</t>
@@ -3336,7 +3249,6 @@
           <t>매우 강력하나 라벨 이슈</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3344,7 +3256,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3386,7 +3297,6 @@
           <t>섬유·fat replacer·바디(저당 고형분)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3394,7 +3304,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3436,7 +3345,6 @@
           <t>벌킹·약한 FPD</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3444,7 +3352,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3486,7 +3393,6 @@
           <t>가용성 섬유·바디(당 아님)</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3494,7 +3400,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3536,7 +3441,6 @@
           <t>heat-shock/용해저항·fat-like</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3544,7 +3448,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3586,7 +3489,6 @@
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3594,7 +3496,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>벌킹/섬유</t>
@@ -3636,7 +3537,6 @@
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3644,7 +3544,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>풍미</t>
@@ -3676,13 +3575,11 @@
           <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>기본 향</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3690,7 +3587,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>풍미</t>
@@ -3732,7 +3628,6 @@
           <t>쌀 풍미 보강(base와 별개시)</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3740,7 +3635,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>풍미</t>
@@ -3772,13 +3666,11 @@
           <t>[검토 2026-08-31 · 값 수정] 소금에 상한폭을 두는 이유는 이해하기 힘들다. · 이전: 표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>풍미증진·리치니스↑(소량)</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3786,7 +3678,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>풍미</t>
@@ -3828,7 +3719,6 @@
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3836,7 +3726,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>풍미</t>
@@ -3868,7 +3757,6 @@
           <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
@@ -3886,7 +3774,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -3907,16 +3794,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3924,7 +3806,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -3945,16 +3826,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3962,7 +3838,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -3983,16 +3858,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4000,7 +3870,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -4021,16 +3890,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4038,7 +3902,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -4059,16 +3922,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4076,7 +3934,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -4097,9 +3954,6 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓</t>
@@ -4110,7 +3964,6 @@
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4118,7 +3971,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -4139,16 +3991,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>보존제(미생물) — 물성 후 단계</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4156,7 +4003,6 @@
           <t>icecream</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>제외/후순위</t>
@@ -4177,16 +4023,11 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>관능·물성 효과 없음</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>beverage_rice_milk</t>
+          <t>RV_rice_milk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>권장</t>
+          <t>제한</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -720,6 +720,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>sweet↑ body↑</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>총칭 자리표시자 (layerC2_ext_his_split.yaml, 2026-08-31 결정). 새 배합에는 스테비아·수크랄로스 등 개별 ID 를 쓸 것. 실측 18건 중 1건에만 있어 ID 는 남긴다</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">

--- a/data/palette.xlsx
+++ b/data/palette.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -479,9 +479,9 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,22 +525,37 @@
           <t>상한</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>통상</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>통상출처</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>통상근거</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>범위근거</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>담당축</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
@@ -578,17 +593,17 @@
       <c r="H2" t="n">
         <v>25.7566</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>sweet↑ body↑</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -626,12 +641,12 @@
       <c r="H3" t="n">
         <v>5.8038</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>실측 18건 중 12건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -669,12 +684,12 @@
       <c r="H4" t="n">
         <v>3.4423</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>실측 18건 중 10건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -712,22 +727,22 @@
       <c r="H5" t="n">
         <v>0.0556</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>실측 18건 중 1건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>sweet↑ body↑</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>총칭 자리표시자 (layerC2_ext_his_split.yaml, 2026-08-31 결정). 새 배합에는 스테비아·수크랄로스 등 개별 ID 를 쓸 것. 실측 18건 중 1건에만 있어 ID 는 남긴다</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -765,12 +780,12 @@
       <c r="H6" t="n">
         <v>1.6098</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -808,17 +823,17 @@
       <c r="H7" t="n">
         <v>6.7416</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>실측 18건 중 14건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>body↑ creaminess↑</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -856,12 +871,12 @@
       <c r="H8" t="n">
         <v>2.4646</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -899,17 +914,17 @@
       <c r="H9" t="n">
         <v>64.39149999999999</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>sweet↑ cooked_rice↑ body↑</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -947,12 +962,12 @@
       <c r="H10" t="n">
         <v>1.2</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정]  · 이전: 실측 18건 전부에 사용 — 사용 범위, 검토 필요</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -990,17 +1005,17 @@
       <c r="H11" t="n">
         <v>9.074400000000001</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>실측 18건 중 4건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>rancid_oxidized↑ body↑ creaminess↑</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -1038,12 +1053,12 @@
       <c r="H12" t="n">
         <v>3.1192</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>실측 18건 중 16건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -1081,17 +1096,17 @@
       <c r="H13" t="n">
         <v>0.5562</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>실측 18건 중 7건에만 사용 — 선택 재료라 하한 0, 상한은 최대 사용량. 검토 필요</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>슬롯·등급 확인 필요</t>
         </is>
@@ -1134,17 +1149,17 @@
       <c r="H14" t="n">
         <v>5</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -1187,17 +1202,17 @@
       <c r="H15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -1240,17 +1255,17 @@
       <c r="H16" t="n">
         <v>5</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -1293,17 +1308,17 @@
       <c r="H17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>[검토 2026-08-31] 저당 아이스크림 기준. '목적에 따라 상한/하한이 바뀐다 — 저당은 상한 5, 하한 0' 지적 반영. 기본 행(일반)은 그대로 두고 이 행이 덮는다.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -1341,17 +1356,17 @@
       <c r="H18" t="n">
         <v>14</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · 필수 base 13% 고정 부근</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>제품 필수 base — 쌀 풍미+고형분. 내재 당류량 확정 필요(저당 회계)</t>
         </is>
@@ -1389,17 +1404,17 @@
       <c r="H19" t="n">
         <v>14</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 유지방 대체 주력. 6% 미만이면 크리미가 안 서고, 14% 넘으면 기름진 느낌</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
@@ -1437,17 +1452,17 @@
       <c r="H20" t="n">
         <v>14</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 정제야자유</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>유지방 유사 프로파일·구조; 정제형은 무향·산화안정</t>
         </is>
@@ -1485,17 +1500,17 @@
       <c r="H21" t="n">
         <v>10</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 분말지방. 믹스 편의</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>분말지방; 믹스 편의·크리미</t>
         </is>
@@ -1533,17 +1548,17 @@
       <c r="H22" t="n">
         <v>8</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 지방+유화 겸. 당을 소량 동반</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
@@ -1581,17 +1596,17 @@
       <c r="H23" t="n">
         <v>8</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 프리마. 당 소량 기여를 저당 회계에 반영할 것</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>지방+유화 겸(크리머). 프리마는 당 소량 기여</t>
         </is>
@@ -1629,17 +1644,17 @@
       <c r="H24" t="n">
         <v>5</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 경질지방 — 소량 구조재. 과하면 왁시</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>경질지방→용해저항·구조(소량 구조재)</t>
         </is>
@@ -1677,17 +1692,17 @@
       <c r="H25" t="n">
         <v>12</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 범용 식물지방. 코코넛유보다 보조 위치</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>범용 식물지방</t>
         </is>
@@ -1725,17 +1740,17 @@
       <c r="H26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · PUFA 산화 관리 필요 — 상한을 낮게</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>쌀 뉘앙스 보강 가능; PUFA 산화 관리 필요</t>
         </is>
@@ -1773,17 +1788,17 @@
       <c r="H27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 산화안정 좋은 액상유</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>산화안정 좋은 액상유</t>
         </is>
@@ -1821,17 +1836,17 @@
       <c r="H28" t="n">
         <v>8</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 산화 취약 — 산화취 위험. 고올레산형으로 대체 권장</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>산화 취약 — 산화취 위험, 지양</t>
         </is>
@@ -1863,12 +1878,12 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
@@ -1906,17 +1921,17 @@
       <c r="H30" t="n">
         <v>15</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 알룰로스</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>저당 linchpin — 단맛+바디+빙점강하, 쿨링 없음</t>
         </is>
@@ -1954,17 +1969,17 @@
       <c r="H31" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · 8% 넘으면 쿨링 오프노트가 뚜렷해진다(HANDOFF 경고)</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>보조 감미·FPD; 쿨링 오프노트 주의</t>
         </is>
@@ -2002,17 +2017,17 @@
       <c r="H32" t="n">
         <v>0.08</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 삭제] HIS는 쪼개기로 했었지.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>단맛 보강 극소량(벌크·FPD 없음)</t>
         </is>
@@ -2050,17 +2065,17 @@
       <c r="H33" t="n">
         <v>25</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정] 목적에 따라 상한/하한이 바뀐다. 지금껀 일반 아이스크림 기준으로, 저당 아이스크림은 상한이 5, 하한은 0이된다. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 저당 목표와 상충하나 FPD·바디 목적 최소량은 필요할 수 있다</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -2098,17 +2113,17 @@
       <c r="H34" t="n">
         <v>10</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. 같은 이유</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -2146,17 +2161,17 @@
       <c r="H35" t="n">
         <v>5</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류. FPD 가 설탕보다 강해 소량으로도 효과</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -2194,17 +2209,17 @@
       <c r="H36" t="n">
         <v>10</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정] 당류 재료는 설탕과 연계된 상한을 지닌다. 특히, 저당이 목적일 경우는 더더욱 그러함. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 당류(쌀조청)</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>당류 — 저당 목표와 상충. FPD·바디 목적 최소만</t>
         </is>
@@ -2242,17 +2257,17 @@
       <c r="H37" t="n">
         <v>3.5</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 유화·기포·바디. 3.5% 넘으면 콩 오프노트</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>유화·기포·바디 (단백 결론: 대두단백)</t>
         </is>
@@ -2290,17 +2305,17 @@
       <c r="H38" t="n">
         <v>3.5</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 대체 식물단백. 오프노트는 대두보다 강한 편</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>대체 식물단백</t>
         </is>
@@ -2338,17 +2353,17 @@
       <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 보류] 쌀단백은 공급사에 따라 편차가 굉장히 큰 재료. 일단 보류 후 데이터에 의존 · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 가용성 낮고 그릿티 — 대두단백으로 대체 결론(HANDOFF)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>가용성 낮음·그릿티 → 대두로 대체</t>
         </is>
@@ -2380,12 +2395,12 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>동물성(비건 아님)</t>
         </is>
@@ -2423,17 +2438,17 @@
       <c r="H41" t="n">
         <v>0.35</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>HANDOFF §3.3 · iter0 레버 구아검</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>얼음결정 억제 주력</t>
         </is>
@@ -2471,17 +2486,17 @@
       <c r="H42" t="n">
         <v>0.3</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 구아와 시너지. 0.3% 넘으면 검성</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>구아와 시너지·크리미</t>
         </is>
@@ -2519,17 +2534,17 @@
       <c r="H43" t="n">
         <v>0.05</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 2차 안정제 — 유청분리 방지용 극소량</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
@@ -2567,17 +2582,17 @@
       <c r="H44" t="n">
         <v>0.05</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 같은 역할. 겔화 안 하는 형</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>서스펜션·바디(유청분리 방지)</t>
         </is>
@@ -2615,17 +2630,17 @@
       <c r="H45" t="n">
         <v>3</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정]  · 이전: 표준 사용량(초안) — 검토 필요 · HPMC. 오버런·용해저항·동결해동</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓ icy↓</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>오버런·용해저항·동결해동 안정</t>
         </is>
@@ -2663,17 +2678,17 @@
       <c r="H46" t="n">
         <v>0.2</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 온톨로지 limitations: '&gt; ~0.5% -&gt; slimy/stringy'. 그보다 훨씬 낮게 잡음</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>소량 점도(과량시 검성 주의)</t>
         </is>
@@ -2711,17 +2726,17 @@
       <c r="H47" t="n">
         <v>0.3</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 점도·수분결합</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>점도·수분결합</t>
         </is>
@@ -2759,17 +2774,17 @@
       <c r="H48" t="n">
         <v>0.1</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 극소량 구조. 과하면 부서지는 겔</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>겔화, 극소량 구조</t>
         </is>
@@ -2807,17 +2822,17 @@
       <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 바디·fat replacer. 과하면 전분 느낌</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓ body↑</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>바디·fat replacer</t>
         </is>
@@ -2855,17 +2870,17 @@
       <c r="H50" t="n">
         <v>0.4</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 아이스크림 표준 유화제</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↑</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>아이스크림 표준 유화제(식물성 선택)</t>
         </is>
@@ -2903,17 +2918,17 @@
       <c r="H51" t="n">
         <v>0.25</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 저HLB. 총량 0.3% 안팎에서 고HLB와 비율 조절</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↑</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>저HLB→지방 부분응집(건조·크리미·용해지연)</t>
         </is>
@@ -2951,17 +2966,17 @@
       <c r="H52" t="n">
         <v>0.25</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 고HLB. DMG95 와 페어링</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>고HLB→미세 유화(저HLB와 페어링)</t>
         </is>
@@ -2999,17 +3014,17 @@
       <c r="H53" t="n">
         <v>0.25</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 중HLB 보조</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
@@ -3047,17 +3062,17 @@
       <c r="H54" t="n">
         <v>0.5</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↑</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
@@ -3095,17 +3110,17 @@
       <c r="H55" t="n">
         <v>0.5</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 보류] 실사용해 본 적 없는 재료. 우선 보류 · 이전: 표준 사용량(초안) — 검토 필요 · 클린라벨 보조 유화</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>중HLB·클린라벨 보조 유화</t>
         </is>
@@ -3143,17 +3158,17 @@
       <c r="H56" t="n">
         <v>0.5</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 메모만] 유화제의 당담축 재고 필요. Creaminess 뿐 아니라, 기름 맛 (oxidized and nutty 등), 물성 전반 등 다양한 효과가 있는데 당담축이 하나 뿐임. · 이전: 표준 사용량(초안) — 검토 필요 · 보조 유화</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
@@ -3191,17 +3206,17 @@
       <c r="H57" t="n">
         <v>5</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정] 에멀에이드와 현미호분추출분말은 다른 재료임. 이 칸은 에멀에이드로 변경 · 이전: 표준 사용량(초안) — 검토 필요 · 현미호분추출분말 — 유화 겸 풍미. 음료 실측에서 1.2~2.5% 사용</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>보조 유화(현미분말은 풍미 겸)</t>
         </is>
@@ -3239,17 +3254,17 @@
       <c r="H58" t="n">
         <v>0.08</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 보류] 식품업계에서는 잘 쓰이지 않음. · 이전: 표준 사용량(초안) — 검토 필요 · 제한 등급 · 매우 강력하나 라벨 이슈. 쓴다면 극소량</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>매우 강력하나 라벨 이슈</t>
         </is>
@@ -3287,17 +3302,17 @@
       <c r="H59" t="n">
         <v>8</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 보류] 제조사에 따라 성능 편차가 큼 · 이전: 표준 사용량(초안) — 검토 필요 · 섬유·fat replacer. 과하면 소화 불편</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>creaminess↑ body↑</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>섬유·fat replacer·바디(저당 고형분)</t>
         </is>
@@ -3335,17 +3350,17 @@
       <c r="H60" t="n">
         <v>8</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 벌킹·약한 FPD. 같은 이유로 상한</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>벌킹·약한 FPD</t>
         </is>
@@ -3383,17 +3398,17 @@
       <c r="H61" t="n">
         <v>8</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 가용성 섬유. 당류 미산입</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>가용성 섬유·바디(당 아님)</t>
         </is>
@@ -3431,17 +3446,17 @@
       <c r="H62" t="n">
         <v>1</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · heat-shock 저항·fat-like</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>heat-shock/용해저항·fat-like</t>
         </is>
@@ -3479,17 +3494,17 @@
       <c r="H63" t="n">
         <v>8</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 고형분. GI 유의</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>creaminess↑ hardness↓ body↑</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
@@ -3527,17 +3542,17 @@
       <c r="H64" t="n">
         <v>8</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 고형분</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>고형분(말토덱스트린 GI 유의)</t>
         </is>
@@ -3575,12 +3590,12 @@
       <c r="H65" t="n">
         <v>0.6</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 기본 향</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>기본 향</t>
         </is>
@@ -3618,17 +3633,17 @@
       <c r="H66" t="n">
         <v>3</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 쌀 풍미 보강</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>body↑</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>쌀 풍미 보강(base와 별개시)</t>
         </is>
@@ -3666,12 +3681,12 @@
       <c r="H67" t="n">
         <v>1.5</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>[검토 2026-08-31 · 값 수정] 소금에 상한폭을 두는 이유는 이해하기 힘들다. · 이전: 표준 사용량(초안) — 검토 필요 · 풍미증진. 0.2% 넘으면 짠맛이 인지된다</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>풍미증진·리치니스↑(소량)</t>
         </is>
@@ -3709,17 +3724,17 @@
       <c r="H68" t="n">
         <v>15</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시. 수분·당을 동반</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>sweet↑ hardness↓</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
@@ -3757,17 +3772,17 @@
       <c r="H69" t="n">
         <v>0.3</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>표준 사용량(초안) — 검토 필요 · 딸기 변형 시</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>딸기 변형 시</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>ID 확인 필요</t>
         </is>
@@ -3799,7 +3814,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
@@ -3831,7 +3846,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
@@ -3863,7 +3878,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>산 — 과일맛 아니면 불필요</t>
         </is>
@@ -3895,7 +3910,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
@@ -3927,7 +3942,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
@@ -3959,12 +3974,12 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>creaminess↑ icy↓</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>pH/칼슘 — 기본 배합 불필요</t>
         </is>
@@ -3996,7 +4011,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>보존제(미생물) — 물성 후 단계</t>
         </is>
@@ -4028,7 +4043,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>관능·물성 효과 없음</t>
         </is>
